--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E67168F-AD47-4301-8020-C33B61F3F315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E04000-B638-4C78-8867-8090C03733FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30720" yWindow="360" windowWidth="61332" windowHeight="15300" tabRatio="858" firstSheet="21" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="858" firstSheet="40" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview_AZ" sheetId="8" r:id="rId1"/>
@@ -68,7 +68,8 @@
     <sheet name="bycatch_NrS" sheetId="57" r:id="rId53"/>
     <sheet name="bycatch_NwS" sheetId="58" r:id="rId54"/>
     <sheet name="bycatch_ONA" sheetId="59" r:id="rId55"/>
-    <sheet name="glossary" sheetId="17" r:id="rId56"/>
+    <sheet name="mixfish_scenarios" sheetId="60" r:id="rId56"/>
+    <sheet name="glossary" sheetId="17" r:id="rId57"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -91,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="1013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="1035">
   <si>
     <t>section</t>
   </si>
@@ -4896,6 +4897,72 @@
 Multiannual bycatch rates were estimated for 3 marine mammal species in one métier. The highest bycatch rate was estimated for harbor porpoise in set gillnets, followed by harbor seal in set gillnets and grey seal in set gillnets. &lt;/p&gt;
 &lt;p&gt;
 Multiannual bycatch rates were estimated for 5 seabird species in one métier. The highest bycatch rate was estimated for northern fulmar in set gillnets, followed by common guillemot in set gillnets and razorbill in set gillnets.  &lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Mixed fisheries effort assumption</t>
+  </si>
+  <si>
+    <t>Minimum (min)</t>
+  </si>
+  <si>
+    <t>For each fleet, fishing in forecast year stops when the catch for any one of the stocks meets its stock share. This scenario is the most precautionary option and can highlight some potential “choke species” issues.</t>
+  </si>
+  <si>
+    <t>Maximum (max)</t>
+  </si>
+  <si>
+    <t>For each fleet, fishing in forecast year continues until all its stock shares have been caught. This option illustrates the degree of overshoot of the single-stock advice if fishing is not restricted by the fleet stock shares.</t>
+  </si>
+  <si>
+    <t>Status quo effort (sq_E)</t>
+  </si>
+  <si>
+    <t>The effort of each fleet in forecast year is set equal to the effort in the most recent year (2024).</t>
+  </si>
+  <si>
+    <t>case_study</t>
+  </si>
+  <si>
+    <t>Minimum including ranges (min_range)</t>
+  </si>
+  <si>
+    <t>Same as “min” scenario</t>
+  </si>
+  <si>
+    <t>Minimum excluding zero-catch advice stocks (min_exzero)</t>
+  </si>
+  <si>
+    <t>For each fleet, fishing in forecast year stops when the catch for any one of the stocks meets its stock share, ignoring cod, which has zero- catch advice. This scenario illustrates the effect of fishing on the most limiting stock with non-zero-catch advice.</t>
+  </si>
+  <si>
+    <t>Celtic Sea</t>
+  </si>
+  <si>
+    <t>Greater North Sea</t>
+  </si>
+  <si>
+    <t>Irish Sea</t>
+  </si>
+  <si>
+    <t>Single-stock advice for cod (cod-is), haddock (had-is), Norway lobster (nep-is), sole (sol-is), and whiting (whg-is)</t>
+  </si>
+  <si>
+    <t>For each fleet, fishing in forercast year stops when the catch of the scenario-specified stock meets its stock share. Fleets which do not catch the scenario-specified stock follow a status quo effort assumption (as described for the “sq_E” scenario). In all these single-stock advice scenarios, fleets that target sole (all beam trawls and Belgian otter trawls) are also restricted by their stock share of sole in addition to the scenario-specified stock.</t>
+  </si>
+  <si>
+    <t>Single-stock advice for black-bellied anglerfish (ank-iw), hake (hke-iw), four-spot megrim (ldb-iw), megrim (meg-iw), and white anglerfish (mon-iw)</t>
+  </si>
+  <si>
+    <t>For each fleet, fishing in 2024 stops when the catch of the scenario-specified stock meets its stock share*, regardless of other catches. Fleets which do not catch the scenario-specified stock follow a status quo effort assumption (as described for the “sq_E” scenario).</t>
+  </si>
+  <si>
+    <t>Bay of Biscay</t>
+  </si>
+  <si>
+    <t>Iberian Waters</t>
   </si>
 </sst>
 </file>
@@ -7396,6 +7463,296 @@
 </file>
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F161C678-5E6F-46CF-B9B5-1EAF42C93FC4}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="49" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="208.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5EC4FE-E411-4E36-B8C3-47DB4028DB0F}">
   <dimension ref="A1:C314"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E04000-B638-4C78-8867-8090C03733FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CB81DB-B56C-456B-8812-7AF1615CAF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="858" firstSheet="40" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="1035">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="1040">
   <si>
     <t>section</t>
   </si>
@@ -4963,6 +4963,21 @@
   </si>
   <si>
     <t>Iberian Waters</t>
+  </si>
+  <si>
+    <t>Basis for catch limit in forecast year</t>
+  </si>
+  <si>
+    <t>ICES catch advice</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>Catches corresponding to FMSY upper for stocks in good status (SSB ≥ MSY B trigger) and reduced FMSY advice levels (F MSY × SSB/MSY B trigger) for the other stocks (including zero-catch advice).</t>
+  </si>
+  <si>
+    <t>ICES catch advice for stocks with a non- zero-catch advice; no catch limit assumed for stocks with a zero-catch advice.</t>
   </si>
 </sst>
 </file>
@@ -7464,15 +7479,16 @@
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F161C678-5E6F-46CF-B9B5-1EAF42C93FC4}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="208.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="91" customWidth="1"/>
+    <col min="3" max="3" width="73.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1013</v>
       </c>
@@ -7480,32 +7496,41 @@
         <v>1014</v>
       </c>
       <c r="C1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D1" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1015</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D2" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1017</v>
       </c>
       <c r="B3" t="s">
         <v>1018</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D3" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1019</v>
       </c>
@@ -7513,10 +7538,13 @@
         <v>1020</v>
       </c>
       <c r="C4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D4" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1022</v>
       </c>
@@ -7524,10 +7552,13 @@
         <v>1023</v>
       </c>
       <c r="C5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D5" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1024</v>
       </c>
@@ -7535,32 +7566,41 @@
         <v>1025</v>
       </c>
       <c r="C6" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D6" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1015</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D7" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1017</v>
       </c>
       <c r="B8" t="s">
         <v>1018</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D8" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1019</v>
       </c>
@@ -7568,10 +7608,13 @@
         <v>1020</v>
       </c>
       <c r="C9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D9" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1022</v>
       </c>
@@ -7579,43 +7622,52 @@
         <v>1023</v>
       </c>
       <c r="C10" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D10" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1024</v>
       </c>
       <c r="B11" t="s">
         <v>1025</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1015</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D12" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1017</v>
       </c>
       <c r="B13" t="s">
         <v>1018</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D13" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1019</v>
       </c>
@@ -7623,10 +7675,13 @@
         <v>1020</v>
       </c>
       <c r="C14" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D14" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1022</v>
       </c>
@@ -7634,43 +7689,52 @@
         <v>1023</v>
       </c>
       <c r="C15" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D15" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1029</v>
       </c>
       <c r="B16" t="s">
         <v>1030</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1015</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D17" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1017</v>
       </c>
       <c r="B18" t="s">
         <v>1018</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D18" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1019</v>
       </c>
@@ -7678,10 +7742,13 @@
         <v>1020</v>
       </c>
       <c r="C19" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D19" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1022</v>
       </c>
@@ -7689,43 +7756,55 @@
         <v>1023</v>
       </c>
       <c r="C20" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D20" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1031</v>
       </c>
       <c r="B21" t="s">
         <v>1032</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D21" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1015</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D22" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1017</v>
       </c>
       <c r="B23" t="s">
         <v>1018</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D23" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1019</v>
       </c>
@@ -7733,17 +7812,23 @@
         <v>1020</v>
       </c>
       <c r="C24" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D24" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1022</v>
       </c>
       <c r="B25" t="s">
         <v>1023</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D25" t="s">
         <v>1033</v>
       </c>
     </row>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CB81DB-B56C-456B-8812-7AF1615CAF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5843ABC9-0D21-4BD8-91B6-FEF3484894D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="858" firstSheet="40" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" firstSheet="47" activeTab="60" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview_AZ" sheetId="8" r:id="rId1"/>
@@ -69,7 +69,12 @@
     <sheet name="bycatch_NwS" sheetId="58" r:id="rId54"/>
     <sheet name="bycatch_ONA" sheetId="59" r:id="rId55"/>
     <sheet name="mixfish_scenarios" sheetId="60" r:id="rId56"/>
-    <sheet name="glossary" sheetId="17" r:id="rId57"/>
+    <sheet name="mixfish_NrS" sheetId="61" r:id="rId57"/>
+    <sheet name="mixfish_CSx" sheetId="62" r:id="rId58"/>
+    <sheet name="mixfish_IrS" sheetId="63" r:id="rId59"/>
+    <sheet name="mixfish_BoB" sheetId="64" r:id="rId60"/>
+    <sheet name="mixfish_IW" sheetId="65" r:id="rId61"/>
+    <sheet name="glossary" sheetId="17" r:id="rId62"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -92,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="1051">
   <si>
     <t>section</t>
   </si>
@@ -4979,12 +4984,45 @@
   <si>
     <t>ICES catch advice for stocks with a non- zero-catch advice; no catch limit assumed for stocks with a zero-catch advice.</t>
   </si>
+  <si>
+    <t>plot1</t>
+  </si>
+  <si>
+    <t>plot2</t>
+  </si>
+  <si>
+    <t>plot3</t>
+  </si>
+  <si>
+    <t>plot4</t>
+  </si>
+  <si>
+    <t>plot5</t>
+  </si>
+  <si>
+    <t>plot6</t>
+  </si>
+  <si>
+    <t>Mixed-fisheries projections of potential catches by stock and scenario. The solid horizontal line indicates the single-stock catch advice. Green shading indicates catches at or below the advice; yellow, where present, indicates catches above the advice but within the upper FMSY catch reference; red indicates catches above that reference, or above the advice where no upper reference is shown. Dotted lines indicate catches corresponding to lower and upper FMSY reference points, adjusted for stock status where applicable. Compare the same scenario across stocks to identify trade-offs in achieving single-stock catch advice.</t>
+  </si>
+  <si>
+    <t>Estimated fishing effort required by each fleet to reach its share of the single-stock catch advice. Colours identify stocks; a red border and asterisk indicate the most limiting stock(s) (“choke species”), while a green border indicates the least limiting stock. The dashed line shows status quo effort for reference. Compare bars within each fleet to identify which stocks constrain fishing first and which fishing opportunities may remain unused when that limit is reached.</t>
+  </si>
+  <si>
+    <t>Distribution of landings by métier and stock. Each stacked bar represents a métier; its total height shows landings of the stocks included, and coloured segments show each stock’s contribution. Compare segments within bars to identify the stock composition of each métier, and the same colour across bars to see how a stock’s landings are distributed among métiers. Métier definitions are provided in glossary.</t>
+  </si>
+  <si>
+    <t>Distribution of landings by stock, expressed as a share of total landed weight. Colours identify stocks, and the size of each slice indicates its relative contribution to the landings shown.</t>
+  </si>
+  <si>
+    <t>lorem ipsum</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5045,6 +5083,12 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5415,13 +5459,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C69BDA-CBD4-4A20-96F1-D4184C7A4A9F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
-    <col min="2" max="2" width="152.21875" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="152.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5429,7 +5473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -5437,7 +5481,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -5445,7 +5489,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="144" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -5464,13 +5508,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
-    <col min="2" max="2" width="198.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="198.1796875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5478,7 +5522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -5486,7 +5530,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -5494,7 +5538,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -5510,13 +5554,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{744F2D0C-79DF-4FE3-924E-E680015F9291}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
-    <col min="2" max="2" width="229.77734375" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="229.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5524,7 +5568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -5532,7 +5576,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -5540,7 +5584,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -5556,13 +5600,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2C24DB-5CFD-48C4-BB67-81838BA61C50}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5570,7 +5614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -5578,7 +5622,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -5594,13 +5638,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BBE4C-C868-422D-A432-89141BF78270}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5608,7 +5652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -5616,7 +5660,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -5632,13 +5676,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537C8D36-44B6-40AB-B2F5-C278C8F38BBE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5646,7 +5690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -5654,7 +5698,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -5670,13 +5714,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1208CFA8-0BD4-4A00-92D8-FF2B69E34213}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5684,7 +5728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -5692,7 +5736,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -5708,12 +5752,12 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D76C43-B7D3-42D3-B057-81CA4865142E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="125.5546875" customWidth="1"/>
+    <col min="2" max="2" width="125.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5721,7 +5765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -5729,7 +5773,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="319" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -5745,13 +5789,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C668CA08-39B4-442C-BE86-54D5793A9F15}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5759,7 +5803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -5767,7 +5811,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -5783,13 +5827,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82938685-CEEB-4659-B68E-B225C7C9053C}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5797,7 +5841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -5805,7 +5849,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -5821,13 +5865,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2B002E-5D4B-4A97-8E05-ADA2BC7262BC}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5835,7 +5879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -5843,7 +5887,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -5859,13 +5903,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB4192-B3A0-40C4-9076-17E7860549D0}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
-    <col min="2" max="2" width="253.77734375" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="253.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5873,7 +5917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -5881,7 +5925,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -5889,7 +5933,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -5908,13 +5952,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5922,7 +5966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -5930,7 +5974,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -5946,13 +5990,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35913B4E-3457-4352-AB64-7123F047E008}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5960,7 +6004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -5968,7 +6012,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -5984,13 +6028,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FEA048-930A-43AC-A2F7-E864F3A29AEA}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5998,7 +6042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -6006,7 +6050,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -6023,13 +6067,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDA5AB7-BD7F-4972-B610-8565F27586E1}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="199.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6037,7 +6081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -6045,7 +6089,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -6053,7 +6097,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -6061,7 +6105,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -6075,13 +6119,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A9AAE-7632-44EA-B097-966294B825CF}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="199.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6089,7 +6133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -6097,7 +6141,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -6105,7 +6149,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -6113,7 +6157,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -6126,13 +6170,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6950BB04-C139-4D8C-A7DF-A5C6DE881B95}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="199.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6140,7 +6184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -6148,7 +6192,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -6156,7 +6200,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -6164,7 +6208,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -6177,13 +6221,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0EDBDB-CFB0-452E-9EB1-4612E534D157}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="199.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6191,7 +6235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -6199,7 +6243,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -6207,7 +6251,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -6215,7 +6259,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -6231,13 +6275,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="199.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6245,7 +6289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -6253,7 +6297,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -6261,7 +6305,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -6269,7 +6313,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -6282,13 +6326,13 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFB3DE4-9A8D-444C-8A7F-95843C784F87}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="199.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6296,7 +6340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -6304,7 +6348,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -6312,7 +6356,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -6320,7 +6364,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -6333,13 +6377,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C70DEC-BE18-4032-87AC-08A2E40C3A39}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="199.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6347,7 +6391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -6355,7 +6399,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -6363,7 +6407,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -6371,7 +6415,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -6384,13 +6428,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D16401-415E-4611-9BEF-C11909718B5A}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
-    <col min="2" max="2" width="223.77734375" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="223.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6398,7 +6442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -6406,7 +6450,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -6414,7 +6458,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -6430,13 +6474,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C59D7F3-BDC1-449F-9172-26F24432D1B6}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="199.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6444,7 +6488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -6452,7 +6496,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -6460,7 +6504,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -6468,7 +6512,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -6481,13 +6525,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF4D87F-C244-46B9-BEBE-7BAD5D19F1F9}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="199.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6495,7 +6539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -6503,7 +6547,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -6511,7 +6555,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -6519,7 +6563,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -6532,13 +6576,13 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EFC30CA-8C29-4D4C-B219-684CAC50F683}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="199.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6546,7 +6590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -6554,7 +6598,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -6562,7 +6606,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -6570,7 +6614,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -6583,13 +6627,13 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051B8018-23E1-4D0A-B47D-B5B875F199B2}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="199.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6597,7 +6641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -6605,7 +6649,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -6613,7 +6657,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -6621,7 +6665,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -6637,13 +6681,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6651,7 +6695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -6667,13 +6711,13 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD5BEFF-ABF3-4924-AB24-FF61AF228C0E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6681,7 +6725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -6697,13 +6741,13 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924E1A3D-452D-420C-B25E-B5B00D9E4E1C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6711,7 +6755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -6727,13 +6771,13 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815AD19-E228-474C-9937-3BF8367B118E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6741,7 +6785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -6757,13 +6801,13 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D15E140-89C9-45F3-80F4-6B8F3C0CB47C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6771,7 +6815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -6787,13 +6831,13 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE1070B-144A-405D-8FC5-7DE029CC4010}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6801,7 +6845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -6817,13 +6861,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA59C6F2-69D0-4598-BA12-1B489ABE98B2}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
-    <col min="2" max="2" width="181.44140625" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="181.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6831,7 +6875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -6839,7 +6883,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -6847,7 +6891,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -6863,13 +6907,13 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F29691E-1FE6-43C9-8319-10047CCCEDC2}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6877,7 +6921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -6893,13 +6937,13 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44602A52-179B-4771-A428-8A5F60E9F4E5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6907,7 +6951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -6923,13 +6967,13 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8B149-F3B9-47FC-B67F-BAF2CCCF6F3A}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6937,7 +6981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -6953,13 +6997,13 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407DE1E1-ED4A-4EC4-9635-4F064BD979D5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6967,7 +7011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -6983,13 +7027,13 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD0BC59-9F8E-4902-8633-6FC5285FFBA9}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6997,7 +7041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -7016,13 +7060,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7030,7 +7074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -7038,7 +7082,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -7054,13 +7098,13 @@
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F7DC1EE-86C5-4108-AF46-1519F3819416}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="109.77734375" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="109.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7068,7 +7112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="216" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -7076,7 +7120,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="261" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -7092,13 +7136,13 @@
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC14161-2EAA-48CD-8103-6BBBB2474891}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.33203125" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7106,7 +7150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -7114,7 +7158,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -7130,13 +7174,13 @@
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{432DB22F-F7FA-4CA9-A149-B4C592E95431}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7144,7 +7188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -7152,7 +7196,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="360" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -7168,13 +7212,13 @@
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C770D3C-EBB7-4325-A0BF-2D0A464BBA81}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7182,7 +7226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="377" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -7190,7 +7234,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="406" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -7206,13 +7250,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB1D8E1-BE83-467E-ABE2-EB20A46DABB5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
-    <col min="2" max="2" width="222.21875" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="222.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7220,7 +7264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -7228,7 +7272,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -7236,7 +7280,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -7252,13 +7296,13 @@
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F94F2EB0-C540-42F2-9029-153D236879E0}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="33.5546875" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7266,7 +7310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -7274,7 +7318,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -7290,13 +7334,13 @@
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2174F19C-D9CC-4AA4-AC39-2264F751CA4E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7304,7 +7348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -7312,7 +7356,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="348" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -7328,12 +7372,12 @@
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB1F98BC-569D-4E63-A11C-5D8C488EFFA3}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="35.21875" customWidth="1"/>
+    <col min="2" max="2" width="35.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7341,7 +7385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -7349,7 +7393,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -7365,13 +7409,13 @@
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872AC014-EDC6-46B6-9F04-A4A110CE1015}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="87.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7379,7 +7423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="319" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -7387,7 +7431,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="288" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="290" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -7403,13 +7447,13 @@
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92DCF04D-F322-424A-ABB9-6A9DCAD730DC}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7417,7 +7461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -7425,7 +7469,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="232" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -7441,13 +7485,13 @@
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82D4A72-6C09-4E6C-AC1C-1FD3518043C3}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7455,7 +7499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="290" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -7463,7 +7507,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -7480,15 +7524,15 @@
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F161C678-5E6F-46CF-B9B5-1EAF42C93FC4}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="49" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="91" customWidth="1"/>
-    <col min="3" max="3" width="73.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.54296875" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1013</v>
       </c>
@@ -7502,7 +7546,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1015</v>
       </c>
@@ -7516,7 +7560,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1017</v>
       </c>
@@ -7530,7 +7574,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1019</v>
       </c>
@@ -7544,7 +7588,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1022</v>
       </c>
@@ -7558,7 +7602,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1024</v>
       </c>
@@ -7572,7 +7616,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>1015</v>
       </c>
@@ -7586,7 +7630,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>1017</v>
       </c>
@@ -7600,7 +7644,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>1019</v>
       </c>
@@ -7614,7 +7658,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>1022</v>
       </c>
@@ -7628,7 +7672,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>1024</v>
       </c>
@@ -7639,7 +7683,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>1015</v>
       </c>
@@ -7653,7 +7697,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>1017</v>
       </c>
@@ -7667,7 +7711,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>1019</v>
       </c>
@@ -7681,7 +7725,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>1022</v>
       </c>
@@ -7695,7 +7739,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>1029</v>
       </c>
@@ -7706,7 +7750,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>1015</v>
       </c>
@@ -7720,7 +7764,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>1017</v>
       </c>
@@ -7734,7 +7778,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>1019</v>
       </c>
@@ -7748,7 +7792,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>1022</v>
       </c>
@@ -7762,7 +7806,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>1031</v>
       </c>
@@ -7776,7 +7820,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>1015</v>
       </c>
@@ -7790,7 +7834,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>1017</v>
       </c>
@@ -7804,7 +7848,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>1019</v>
       </c>
@@ -7818,7 +7862,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>1022</v>
       </c>
@@ -7838,18 +7882,420 @@
 </file>
 
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE3627B5-0F76-48D8-BA85-6CE86B77633D}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="255.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C029B621-D1FB-4847-B522-7D7E37797B55}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="255.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1C0998B-0723-429C-94FD-4E3512F00B49}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="255.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D6F23-1F00-43DA-8201-777B854F56F6}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="137.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="400" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.4">
+      <c r="B5" s="5"/>
+    </row>
+    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.4">
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C0FA9E5-AB5A-4955-88F6-1729857A962F}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="255.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C04D841-7403-4D2B-AC81-1AB38844115A}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="255.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5EC4FE-E411-4E36-B8C3-47DB4028DB0F}">
   <dimension ref="A1:C314"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="168.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.77734375" customWidth="1"/>
-    <col min="17" max="17" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="168.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.81640625" customWidth="1"/>
+    <col min="17" max="17" width="9.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -7860,7 +8306,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>26</v>
       </c>
@@ -7871,7 +8317,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>40</v>
       </c>
@@ -7882,7 +8328,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
@@ -7893,7 +8339,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
@@ -7904,7 +8350,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>928</v>
       </c>
@@ -7915,7 +8361,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>42</v>
       </c>
@@ -7926,7 +8372,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>18</v>
       </c>
@@ -7937,7 +8383,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
@@ -7948,7 +8394,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>22</v>
       </c>
@@ -7959,7 +8405,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>931</v>
       </c>
@@ -7970,7 +8416,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
         <v>934</v>
       </c>
@@ -7981,7 +8427,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
         <v>937</v>
       </c>
@@ -7992,7 +8438,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>940</v>
       </c>
@@ -8003,7 +8449,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
         <v>943</v>
       </c>
@@ -8014,7 +8460,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
         <v>946</v>
       </c>
@@ -8025,7 +8471,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
         <v>949</v>
       </c>
@@ -8036,7 +8482,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>46</v>
       </c>
@@ -8047,7 +8493,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>15</v>
       </c>
@@ -8058,7 +8504,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>952</v>
       </c>
@@ -8069,7 +8515,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>955</v>
       </c>
@@ -8080,7 +8526,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>958</v>
       </c>
@@ -8091,7 +8537,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>961</v>
       </c>
@@ -8102,7 +8548,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="14" t="s">
         <v>38</v>
       </c>
@@ -8113,7 +8559,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>964</v>
       </c>
@@ -8124,7 +8570,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
         <v>20</v>
       </c>
@@ -8135,7 +8581,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="14" t="s">
         <v>32</v>
       </c>
@@ -8146,7 +8592,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
         <v>28</v>
       </c>
@@ -8157,7 +8603,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
         <v>24</v>
       </c>
@@ -8168,7 +8614,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>967</v>
       </c>
@@ -8179,7 +8625,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>970</v>
       </c>
@@ -8190,7 +8636,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>973</v>
       </c>
@@ -8201,7 +8647,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>976</v>
       </c>
@@ -8212,7 +8658,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>979</v>
       </c>
@@ -8223,7 +8669,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>982</v>
       </c>
@@ -8234,7 +8680,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>985</v>
       </c>
@@ -8245,7 +8691,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>988</v>
       </c>
@@ -8256,7 +8702,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="14" t="s">
         <v>36</v>
       </c>
@@ -8267,7 +8713,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>991</v>
       </c>
@@ -8278,7 +8724,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="14" t="s">
         <v>30</v>
       </c>
@@ -8289,7 +8735,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="14" t="s">
         <v>34</v>
       </c>
@@ -8300,7 +8746,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>44</v>
       </c>
@@ -8311,7 +8757,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="10" t="s">
         <v>63</v>
       </c>
@@ -8322,7 +8768,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
         <v>66</v>
       </c>
@@ -8333,7 +8779,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
         <v>69</v>
       </c>
@@ -8344,7 +8790,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
         <v>72</v>
       </c>
@@ -8355,7 +8801,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
         <v>75</v>
       </c>
@@ -8366,7 +8812,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
         <v>78</v>
       </c>
@@ -8377,7 +8823,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="10" t="s">
         <v>81</v>
       </c>
@@ -8388,7 +8834,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
         <v>84</v>
       </c>
@@ -8399,7 +8845,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="10" t="s">
         <v>87</v>
       </c>
@@ -8410,7 +8856,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
         <v>90</v>
       </c>
@@ -8421,7 +8867,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="10" t="s">
         <v>93</v>
       </c>
@@ -8432,7 +8878,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
         <v>96</v>
       </c>
@@ -8443,7 +8889,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
         <v>99</v>
       </c>
@@ -8454,7 +8900,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
         <v>102</v>
       </c>
@@ -8465,7 +8911,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
         <v>105</v>
       </c>
@@ -8476,7 +8922,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="s">
         <v>108</v>
       </c>
@@ -8487,7 +8933,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
         <v>111</v>
       </c>
@@ -8498,7 +8944,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
         <v>114</v>
       </c>
@@ -8509,7 +8955,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="10" t="s">
         <v>117</v>
       </c>
@@ -8520,7 +8966,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
         <v>120</v>
       </c>
@@ -8531,7 +8977,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="s">
         <v>123</v>
       </c>
@@ -8542,7 +8988,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
         <v>126</v>
       </c>
@@ -8553,7 +8999,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
         <v>129</v>
       </c>
@@ -8564,7 +9010,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
         <v>132</v>
       </c>
@@ -8575,7 +9021,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
         <v>135</v>
       </c>
@@ -8586,7 +9032,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
         <v>138</v>
       </c>
@@ -8597,7 +9043,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
         <v>141</v>
       </c>
@@ -8608,7 +9054,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
         <v>144</v>
       </c>
@@ -8619,7 +9065,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="10" t="s">
         <v>147</v>
       </c>
@@ -8630,7 +9076,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
         <v>150</v>
       </c>
@@ -8641,7 +9087,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
         <v>153</v>
       </c>
@@ -8652,7 +9098,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
         <v>156</v>
       </c>
@@ -8663,7 +9109,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
         <v>159</v>
       </c>
@@ -8674,7 +9120,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
         <v>162</v>
       </c>
@@ -8685,7 +9131,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
         <v>165</v>
       </c>
@@ -8696,7 +9142,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
         <v>168</v>
       </c>
@@ -8707,7 +9153,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
         <v>171</v>
       </c>
@@ -8718,7 +9164,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
         <v>174</v>
       </c>
@@ -8729,7 +9175,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="10" t="s">
         <v>177</v>
       </c>
@@ -8740,7 +9186,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
         <v>180</v>
       </c>
@@ -8751,7 +9197,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
         <v>183</v>
       </c>
@@ -8762,7 +9208,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
         <v>186</v>
       </c>
@@ -8773,7 +9219,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
         <v>189</v>
       </c>
@@ -8784,7 +9230,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
         <v>192</v>
       </c>
@@ -8795,7 +9241,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
         <v>195</v>
       </c>
@@ -8806,7 +9252,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
         <v>198</v>
       </c>
@@ -8817,7 +9263,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="10" t="s">
         <v>201</v>
       </c>
@@ -8828,7 +9274,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="10" t="s">
         <v>204</v>
       </c>
@@ -8839,7 +9285,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="10" t="s">
         <v>207</v>
       </c>
@@ -8850,7 +9296,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
         <v>210</v>
       </c>
@@ -8861,7 +9307,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="10" t="s">
         <v>213</v>
       </c>
@@ -8872,7 +9318,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="10" t="s">
         <v>216</v>
       </c>
@@ -8883,7 +9329,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="10" t="s">
         <v>219</v>
       </c>
@@ -8894,7 +9340,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="10" t="s">
         <v>222</v>
       </c>
@@ -8905,7 +9351,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
         <v>225</v>
       </c>
@@ -8916,7 +9362,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
         <v>228</v>
       </c>
@@ -8927,7 +9373,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="10" t="s">
         <v>231</v>
       </c>
@@ -8938,7 +9384,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
         <v>234</v>
       </c>
@@ -8949,7 +9395,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="10" t="s">
         <v>237</v>
       </c>
@@ -8960,7 +9406,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
         <v>240</v>
       </c>
@@ -8971,7 +9417,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="10" t="s">
         <v>243</v>
       </c>
@@ -8982,7 +9428,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="10" t="s">
         <v>246</v>
       </c>
@@ -8993,7 +9439,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="10" t="s">
         <v>249</v>
       </c>
@@ -9004,7 +9450,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="10" t="s">
         <v>252</v>
       </c>
@@ -9015,7 +9461,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="10" t="s">
         <v>255</v>
       </c>
@@ -9026,7 +9472,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
         <v>258</v>
       </c>
@@ -9037,7 +9483,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="10" t="s">
         <v>261</v>
       </c>
@@ -9048,7 +9494,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="10" t="s">
         <v>264</v>
       </c>
@@ -9059,7 +9505,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="10" t="s">
         <v>267</v>
       </c>
@@ -9070,7 +9516,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="10" t="s">
         <v>270</v>
       </c>
@@ -9081,7 +9527,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="10" t="s">
         <v>273</v>
       </c>
@@ -9092,7 +9538,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="10" t="s">
         <v>276</v>
       </c>
@@ -9103,7 +9549,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="10" t="s">
         <v>279</v>
       </c>
@@ -9114,7 +9560,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
         <v>282</v>
       </c>
@@ -9125,7 +9571,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="10" t="s">
         <v>285</v>
       </c>
@@ -9136,7 +9582,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="10" t="s">
         <v>288</v>
       </c>
@@ -9147,7 +9593,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
         <v>291</v>
       </c>
@@ -9158,7 +9604,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="10" t="s">
         <v>294</v>
       </c>
@@ -9169,7 +9615,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="10" t="s">
         <v>297</v>
       </c>
@@ -9180,7 +9626,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="10" t="s">
         <v>300</v>
       </c>
@@ -9191,7 +9637,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="10" t="s">
         <v>303</v>
       </c>
@@ -9202,7 +9648,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
         <v>306</v>
       </c>
@@ -9213,7 +9659,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="10" t="s">
         <v>309</v>
       </c>
@@ -9224,7 +9670,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
         <v>312</v>
       </c>
@@ -9235,7 +9681,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
         <v>315</v>
       </c>
@@ -9246,7 +9692,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="10" t="s">
         <v>318</v>
       </c>
@@ -9257,7 +9703,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="10" t="s">
         <v>321</v>
       </c>
@@ -9268,7 +9714,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
         <v>324</v>
       </c>
@@ -9279,7 +9725,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
         <v>327</v>
       </c>
@@ -9290,7 +9736,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
         <v>330</v>
       </c>
@@ -9301,7 +9747,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="10" t="s">
         <v>333</v>
       </c>
@@ -9312,7 +9758,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="10" t="s">
         <v>336</v>
       </c>
@@ -9323,7 +9769,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="10" t="s">
         <v>339</v>
       </c>
@@ -9334,7 +9780,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="10" t="s">
         <v>342</v>
       </c>
@@ -9345,7 +9791,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="10" t="s">
         <v>345</v>
       </c>
@@ -9356,7 +9802,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="10" t="s">
         <v>348</v>
       </c>
@@ -9367,7 +9813,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="10" t="s">
         <v>351</v>
       </c>
@@ -9378,7 +9824,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="10" t="s">
         <v>354</v>
       </c>
@@ -9389,7 +9835,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="10" t="s">
         <v>357</v>
       </c>
@@ -9400,7 +9846,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="10" t="s">
         <v>360</v>
       </c>
@@ -9411,7 +9857,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="10" t="s">
         <v>363</v>
       </c>
@@ -9422,7 +9868,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="10" t="s">
         <v>366</v>
       </c>
@@ -9433,7 +9879,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="10" t="s">
         <v>369</v>
       </c>
@@ -9444,7 +9890,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="10" t="s">
         <v>372</v>
       </c>
@@ -9455,7 +9901,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="10" t="s">
         <v>375</v>
       </c>
@@ -9466,7 +9912,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="10" t="s">
         <v>378</v>
       </c>
@@ -9477,7 +9923,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="10" t="s">
         <v>381</v>
       </c>
@@ -9488,7 +9934,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="10" t="s">
         <v>384</v>
       </c>
@@ -9499,7 +9945,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="10" t="s">
         <v>387</v>
       </c>
@@ -9510,7 +9956,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="10" t="s">
         <v>390</v>
       </c>
@@ -9521,7 +9967,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="10" t="s">
         <v>393</v>
       </c>
@@ -9532,7 +9978,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="10" t="s">
         <v>396</v>
       </c>
@@ -9543,7 +9989,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="10" t="s">
         <v>399</v>
       </c>
@@ -9554,7 +10000,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="10" t="s">
         <v>402</v>
       </c>
@@ -9565,7 +10011,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="10" t="s">
         <v>405</v>
       </c>
@@ -9576,7 +10022,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="10" t="s">
         <v>408</v>
       </c>
@@ -9587,7 +10033,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="10" t="s">
         <v>411</v>
       </c>
@@ -9598,7 +10044,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="10" t="s">
         <v>414</v>
       </c>
@@ -9609,7 +10055,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="10" t="s">
         <v>417</v>
       </c>
@@ -9620,7 +10066,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="10" t="s">
         <v>420</v>
       </c>
@@ -9631,7 +10077,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="10" t="s">
         <v>423</v>
       </c>
@@ -9642,7 +10088,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="10" t="s">
         <v>426</v>
       </c>
@@ -9653,7 +10099,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="10" t="s">
         <v>429</v>
       </c>
@@ -9664,7 +10110,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="10" t="s">
         <v>432</v>
       </c>
@@ -9675,7 +10121,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="10" t="s">
         <v>435</v>
       </c>
@@ -9686,7 +10132,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="10" t="s">
         <v>438</v>
       </c>
@@ -9697,7 +10143,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="10" t="s">
         <v>441</v>
       </c>
@@ -9708,7 +10154,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="10" t="s">
         <v>444</v>
       </c>
@@ -9719,7 +10165,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="10" t="s">
         <v>447</v>
       </c>
@@ -9730,7 +10176,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="10" t="s">
         <v>450</v>
       </c>
@@ -9741,7 +10187,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="10" t="s">
         <v>453</v>
       </c>
@@ -9752,7 +10198,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="10" t="s">
         <v>456</v>
       </c>
@@ -9763,7 +10209,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="10" t="s">
         <v>459</v>
       </c>
@@ -9774,7 +10220,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="10" t="s">
         <v>462</v>
       </c>
@@ -9785,7 +10231,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="10" t="s">
         <v>465</v>
       </c>
@@ -9796,7 +10242,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="10" t="s">
         <v>468</v>
       </c>
@@ -9807,7 +10253,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="10" t="s">
         <v>471</v>
       </c>
@@ -9818,7 +10264,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="10" t="s">
         <v>474</v>
       </c>
@@ -9829,7 +10275,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="10" t="s">
         <v>477</v>
       </c>
@@ -9840,7 +10286,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="10" t="s">
         <v>480</v>
       </c>
@@ -9851,7 +10297,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="10" t="s">
         <v>483</v>
       </c>
@@ -9862,7 +10308,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="10" t="s">
         <v>486</v>
       </c>
@@ -9873,7 +10319,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="10" t="s">
         <v>489</v>
       </c>
@@ -9884,7 +10330,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="10" t="s">
         <v>492</v>
       </c>
@@ -9895,7 +10341,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="10" t="s">
         <v>495</v>
       </c>
@@ -9906,7 +10352,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="10" t="s">
         <v>498</v>
       </c>
@@ -9917,7 +10363,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="10" t="s">
         <v>501</v>
       </c>
@@ -9928,7 +10374,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="10" t="s">
         <v>504</v>
       </c>
@@ -9939,7 +10385,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="10" t="s">
         <v>507</v>
       </c>
@@ -9950,7 +10396,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="10" t="s">
         <v>510</v>
       </c>
@@ -9961,7 +10407,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="10" t="s">
         <v>513</v>
       </c>
@@ -9972,7 +10418,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" s="10" t="s">
         <v>516</v>
       </c>
@@ -9983,7 +10429,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" s="10" t="s">
         <v>519</v>
       </c>
@@ -9994,7 +10440,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" s="10" t="s">
         <v>522</v>
       </c>
@@ -10005,7 +10451,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" s="10" t="s">
         <v>525</v>
       </c>
@@ -10016,7 +10462,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" s="10" t="s">
         <v>528</v>
       </c>
@@ -10027,7 +10473,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" s="10" t="s">
         <v>531</v>
       </c>
@@ -10038,7 +10484,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" s="10" t="s">
         <v>534</v>
       </c>
@@ -10049,7 +10495,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" s="10" t="s">
         <v>537</v>
       </c>
@@ -10060,7 +10506,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" s="10" t="s">
         <v>540</v>
       </c>
@@ -10071,7 +10517,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" s="10" t="s">
         <v>543</v>
       </c>
@@ -10082,7 +10528,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" s="10" t="s">
         <v>546</v>
       </c>
@@ -10093,7 +10539,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" s="10" t="s">
         <v>549</v>
       </c>
@@ -10104,7 +10550,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" s="10" t="s">
         <v>552</v>
       </c>
@@ -10115,7 +10561,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" s="10" t="s">
         <v>555</v>
       </c>
@@ -10126,7 +10572,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" s="10" t="s">
         <v>558</v>
       </c>
@@ -10137,7 +10583,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" s="10" t="s">
         <v>561</v>
       </c>
@@ -10148,7 +10594,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" s="10" t="s">
         <v>564</v>
       </c>
@@ -10159,7 +10605,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" s="10" t="s">
         <v>567</v>
       </c>
@@ -10170,7 +10616,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" s="10" t="s">
         <v>570</v>
       </c>
@@ -10181,7 +10627,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" s="10" t="s">
         <v>573</v>
       </c>
@@ -10192,7 +10638,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" s="10" t="s">
         <v>576</v>
       </c>
@@ -10203,7 +10649,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" s="10" t="s">
         <v>579</v>
       </c>
@@ -10214,7 +10660,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" s="10" t="s">
         <v>582</v>
       </c>
@@ -10225,7 +10671,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" s="10" t="s">
         <v>585</v>
       </c>
@@ -10236,7 +10682,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" s="10" t="s">
         <v>588</v>
       </c>
@@ -10247,7 +10693,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" s="10" t="s">
         <v>591</v>
       </c>
@@ -10258,7 +10704,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" s="10" t="s">
         <v>594</v>
       </c>
@@ -10269,7 +10715,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" s="10" t="s">
         <v>597</v>
       </c>
@@ -10280,7 +10726,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" s="10" t="s">
         <v>600</v>
       </c>
@@ -10291,7 +10737,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" s="10" t="s">
         <v>603</v>
       </c>
@@ -10302,7 +10748,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" s="10" t="s">
         <v>606</v>
       </c>
@@ -10313,7 +10759,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" s="10" t="s">
         <v>609</v>
       </c>
@@ -10324,7 +10770,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" s="10" t="s">
         <v>612</v>
       </c>
@@ -10335,7 +10781,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" s="10" t="s">
         <v>615</v>
       </c>
@@ -10346,7 +10792,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" s="10" t="s">
         <v>618</v>
       </c>
@@ -10357,7 +10803,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" s="10" t="s">
         <v>621</v>
       </c>
@@ -10368,7 +10814,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" s="10" t="s">
         <v>624</v>
       </c>
@@ -10379,7 +10825,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" s="10" t="s">
         <v>627</v>
       </c>
@@ -10390,7 +10836,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" s="10" t="s">
         <v>630</v>
       </c>
@@ -10401,7 +10847,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" s="10" t="s">
         <v>633</v>
       </c>
@@ -10412,7 +10858,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" s="10" t="s">
         <v>636</v>
       </c>
@@ -10423,7 +10869,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" s="10" t="s">
         <v>639</v>
       </c>
@@ -10434,7 +10880,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" s="10" t="s">
         <v>642</v>
       </c>
@@ -10445,7 +10891,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" s="10" t="s">
         <v>645</v>
       </c>
@@ -10456,7 +10902,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" s="10" t="s">
         <v>648</v>
       </c>
@@ -10467,7 +10913,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" s="10" t="s">
         <v>651</v>
       </c>
@@ -10478,7 +10924,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" s="10" t="s">
         <v>654</v>
       </c>
@@ -10489,7 +10935,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" s="10" t="s">
         <v>657</v>
       </c>
@@ -10500,7 +10946,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" s="10" t="s">
         <v>660</v>
       </c>
@@ -10511,7 +10957,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" s="10" t="s">
         <v>663</v>
       </c>
@@ -10522,7 +10968,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" s="10" t="s">
         <v>666</v>
       </c>
@@ -10533,7 +10979,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" s="10" t="s">
         <v>669</v>
       </c>
@@ -10544,7 +10990,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" s="10" t="s">
         <v>672</v>
       </c>
@@ -10555,7 +11001,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" s="10" t="s">
         <v>675</v>
       </c>
@@ -10566,7 +11012,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" s="10" t="s">
         <v>678</v>
       </c>
@@ -10577,7 +11023,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" s="10" t="s">
         <v>681</v>
       </c>
@@ -10588,7 +11034,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" s="10" t="s">
         <v>684</v>
       </c>
@@ -10599,7 +11045,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" s="10" t="s">
         <v>687</v>
       </c>
@@ -10610,7 +11056,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" s="10" t="s">
         <v>690</v>
       </c>
@@ -10621,7 +11067,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" s="10" t="s">
         <v>693</v>
       </c>
@@ -10632,7 +11078,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" s="10" t="s">
         <v>696</v>
       </c>
@@ -10643,7 +11089,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" s="10" t="s">
         <v>699</v>
       </c>
@@ -10654,7 +11100,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" s="10" t="s">
         <v>702</v>
       </c>
@@ -10665,7 +11111,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" s="10" t="s">
         <v>705</v>
       </c>
@@ -10676,7 +11122,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" s="10" t="s">
         <v>708</v>
       </c>
@@ -10687,7 +11133,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" s="10" t="s">
         <v>711</v>
       </c>
@@ -10698,7 +11144,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" s="10" t="s">
         <v>714</v>
       </c>
@@ -10709,7 +11155,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" s="10" t="s">
         <v>717</v>
       </c>
@@ -10720,7 +11166,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" s="10" t="s">
         <v>720</v>
       </c>
@@ -10731,7 +11177,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" s="10" t="s">
         <v>723</v>
       </c>
@@ -10742,7 +11188,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" s="10" t="s">
         <v>726</v>
       </c>
@@ -10753,7 +11199,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" s="10" t="s">
         <v>729</v>
       </c>
@@ -10764,7 +11210,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" s="10" t="s">
         <v>732</v>
       </c>
@@ -10775,7 +11221,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" s="10" t="s">
         <v>735</v>
       </c>
@@ -10786,7 +11232,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" s="10" t="s">
         <v>738</v>
       </c>
@@ -10797,7 +11243,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" s="10" t="s">
         <v>741</v>
       </c>
@@ -10808,7 +11254,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" s="10" t="s">
         <v>744</v>
       </c>
@@ -10819,7 +11265,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" s="10" t="s">
         <v>747</v>
       </c>
@@ -10830,7 +11276,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" s="10" t="s">
         <v>750</v>
       </c>
@@ -10841,7 +11287,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" s="10" t="s">
         <v>753</v>
       </c>
@@ -10852,7 +11298,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" s="10" t="s">
         <v>756</v>
       </c>
@@ -10863,7 +11309,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" s="10" t="s">
         <v>759</v>
       </c>
@@ -10874,7 +11320,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" s="10" t="s">
         <v>762</v>
       </c>
@@ -10885,7 +11331,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" s="10" t="s">
         <v>765</v>
       </c>
@@ -10896,7 +11342,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" s="10" t="s">
         <v>768</v>
       </c>
@@ -10907,7 +11353,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" s="10" t="s">
         <v>771</v>
       </c>
@@ -10918,7 +11364,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" s="10" t="s">
         <v>774</v>
       </c>
@@ -10929,7 +11375,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" s="10" t="s">
         <v>777</v>
       </c>
@@ -10940,7 +11386,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" s="10" t="s">
         <v>780</v>
       </c>
@@ -10951,7 +11397,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" s="10" t="s">
         <v>783</v>
       </c>
@@ -10962,7 +11408,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" s="10" t="s">
         <v>786</v>
       </c>
@@ -10973,7 +11419,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" s="10" t="s">
         <v>789</v>
       </c>
@@ -10984,7 +11430,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" s="10" t="s">
         <v>792</v>
       </c>
@@ -10995,7 +11441,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" s="10" t="s">
         <v>795</v>
       </c>
@@ -11006,7 +11452,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" s="10" t="s">
         <v>798</v>
       </c>
@@ -11017,7 +11463,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" s="10" t="s">
         <v>801</v>
       </c>
@@ -11028,7 +11474,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" s="10" t="s">
         <v>804</v>
       </c>
@@ -11039,7 +11485,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" s="10" t="s">
         <v>807</v>
       </c>
@@ -11050,7 +11496,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" s="10" t="s">
         <v>810</v>
       </c>
@@ -11061,7 +11507,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" s="10" t="s">
         <v>813</v>
       </c>
@@ -11072,7 +11518,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" s="10" t="s">
         <v>816</v>
       </c>
@@ -11083,7 +11529,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" s="10" t="s">
         <v>819</v>
       </c>
@@ -11094,7 +11540,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" s="10" t="s">
         <v>822</v>
       </c>
@@ -11105,7 +11551,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" s="10" t="s">
         <v>825</v>
       </c>
@@ -11116,7 +11562,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" s="10" t="s">
         <v>828</v>
       </c>
@@ -11127,7 +11573,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" s="10" t="s">
         <v>831</v>
       </c>
@@ -11138,7 +11584,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" s="10" t="s">
         <v>834</v>
       </c>
@@ -11149,7 +11595,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" s="10" t="s">
         <v>837</v>
       </c>
@@ -11160,7 +11606,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" s="10" t="s">
         <v>840</v>
       </c>
@@ -11171,7 +11617,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" s="10" t="s">
         <v>843</v>
       </c>
@@ -11182,7 +11628,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" s="10" t="s">
         <v>846</v>
       </c>
@@ -11193,7 +11639,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" s="10" t="s">
         <v>849</v>
       </c>
@@ -11204,7 +11650,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" s="10" t="s">
         <v>852</v>
       </c>
@@ -11215,7 +11661,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" s="10" t="s">
         <v>855</v>
       </c>
@@ -11226,7 +11672,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" s="10" t="s">
         <v>858</v>
       </c>
@@ -11237,7 +11683,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" s="10" t="s">
         <v>861</v>
       </c>
@@ -11248,7 +11694,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" s="10" t="s">
         <v>864</v>
       </c>
@@ -11259,7 +11705,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" s="10" t="s">
         <v>867</v>
       </c>
@@ -11270,7 +11716,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" s="10" t="s">
         <v>870</v>
       </c>
@@ -11281,7 +11727,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" s="10" t="s">
         <v>873</v>
       </c>
@@ -11292,7 +11738,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" s="10" t="s">
         <v>876</v>
       </c>
@@ -11314,71 +11760,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D6F23-1F00-43DA-8201-777B854F56F6}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
-    <col min="2" max="2" width="137.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="390" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="5"/>
-    </row>
-    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B7" s="6"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A026B00C-E4B3-4E36-BEA1-AD93DF3D486F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
-    <col min="2" max="2" width="135.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="135.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11386,7 +11777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -11394,7 +11785,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -11402,7 +11793,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -11418,13 +11809,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27175C00-9C85-488E-AAAE-6AE4E23126BD}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
-    <col min="2" max="2" width="114.77734375" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="114.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11432,7 +11823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -11440,7 +11831,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -11448,7 +11839,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -11467,13 +11858,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11481,7 +11872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -11489,7 +11880,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -11497,7 +11888,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5843ABC9-0D21-4BD8-91B6-FEF3484894D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A52C6FD-EFB2-47F0-86A2-1786F28C32DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" firstSheet="47" activeTab="60" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" firstSheet="47" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview_AZ" sheetId="8" r:id="rId1"/>
@@ -7526,7 +7526,7 @@
   <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="49" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="129.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="91" customWidth="1"/>
     <col min="3" max="3" width="73.54296875" customWidth="1"/>
     <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A52C6FD-EFB2-47F0-86A2-1786F28C32DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D88D8A-559B-42EB-B750-BDF08C3A8C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" firstSheet="47" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" firstSheet="48" activeTab="60" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview_AZ" sheetId="8" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="1051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="1052">
   <si>
     <t>section</t>
   </si>
@@ -5015,7 +5015,10 @@
     <t>Distribution of landings by stock, expressed as a share of total landed weight. Colours identify stocks, and the size of each slice indicates its relative contribution to the landings shown.</t>
   </si>
   <si>
-    <t>lorem ipsum</t>
+    <t>Landings composition in terms of volume by operational mixed-fisheries fleet.</t>
+  </si>
+  <si>
+    <t>Allocation of landings from stocks to operational mixed-fisheries métiers and fleets. The width of each flow is proportional to the landing volume.</t>
   </si>
 </sst>
 </file>
@@ -7942,7 +7945,7 @@
         <v>1045</v>
       </c>
       <c r="B7" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
@@ -8013,7 +8016,7 @@
         <v>1045</v>
       </c>
       <c r="B7" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
@@ -8082,7 +8085,7 @@
         <v>1045</v>
       </c>
       <c r="B7" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
@@ -8206,7 +8209,7 @@
         <v>1045</v>
       </c>
       <c r="B7" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
@@ -8275,7 +8278,7 @@
         <v>1045</v>
       </c>
       <c r="B7" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
